--- a/sampleData/Checklist for Indentor - STANDARD TERMS AND CONDITIONS-f.xlsx
+++ b/sampleData/Checklist for Indentor - STANDARD TERMS AND CONDITIONS-f.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\106388\Desktop\NOTING\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\001\IIT DHARWAD\HAL PURCHASE FORMATS dt 22.06.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BF8738-6CBC-432A-88B9-C1926C62E814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$110</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$3:$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="246">
   <si>
     <t>Sl.</t>
   </si>
@@ -207,9 +206,6 @@
   </si>
   <si>
     <t>CHECK LIST FOR TENDER TERMS AND CONDITIONS</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
   </si>
   <si>
     <t xml:space="preserve">The claims may be set forth:
@@ -876,148 +872,6 @@
 e) Supply of Goods &amp; Services (AMC/CAMC)</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Provisioning File</t>
-  </si>
-  <si>
-    <t>Description of File</t>
-  </si>
-  <si>
-    <t>Subject of File</t>
-  </si>
-  <si>
-    <t>Provide the Subject of File here</t>
-  </si>
-  <si>
-    <t>Direct Project Material or Production Material</t>
-  </si>
-  <si>
-    <t>Indigenisation or Development of Alternate Source of Project Materials</t>
-  </si>
-  <si>
-    <t>Overhead Materials or Commercial Materials, Stock Items</t>
-  </si>
-  <si>
-    <t>Non-stock Items</t>
-  </si>
-  <si>
-    <t>Tool and Gauges</t>
-  </si>
-  <si>
-    <t>Ground Handling Equipment (GHE) - Ground Support Equipment (GSE)- Bay Support Equipment (BSE)</t>
-  </si>
-  <si>
-    <t>Maintenance Spares</t>
-  </si>
-  <si>
-    <t>Vehicle Spares</t>
-  </si>
-  <si>
-    <t>Civil Engineering Requirements</t>
-  </si>
-  <si>
-    <t>Welfare Items</t>
-  </si>
-  <si>
-    <t>Capital Equipment</t>
-  </si>
-  <si>
-    <t>Email/Contact details For Single/Email tender /OEM/Licensor/Proprietary tender/Limited Tenders</t>
-  </si>
-  <si>
-    <t>For floating Tenders having value above INR 5.00Lakhs &amp; up to INR 200.00 Crs, for GTE  outside GeM/Eproc and to Non Clocal/Foreign Suppliers permission is required from concerned Ministry for floating tender.</t>
-  </si>
-  <si>
-    <t>Provisioning CPA as per DOP-2025 &amp; PM Iss-4.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFA Name, Grade &amp; Designation Information
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(To be provided in Remarks Column)</t>
-    </r>
-  </si>
-  <si>
-    <t>Reason for Provisioning</t>
-  </si>
-  <si>
-    <t>Provide the brief reason for Provisoining action</t>
-  </si>
-  <si>
-    <t>Provide Budget Head reference No here</t>
-  </si>
-  <si>
-    <t>Reason for requirements recorded with refrences in Provisioining Note</t>
-  </si>
-  <si>
-    <t>GeM Non Availability Report enclosed for tendering out of GeM &amp; GEM Custom Bidding</t>
-  </si>
-  <si>
-    <t>Submission of Tender In Bid System.</t>
-  </si>
-  <si>
-    <t>GEM-Custom bid</t>
-  </si>
-  <si>
-    <t>Same requirement not Raised within Six Months</t>
-  </si>
-  <si>
-    <t>Same requirement Raised within Six Months of previous MPR leads to splitting of requirement in such cases Permission from Head of Division to be obatined for tendering on account of critical requirement for Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment Modality </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">EMD shall be paid only through SB Collect portal in online mode to Hindustan Aeronautics Ltd, Nasik Division. Further , deposit of the amount in any other form will not be accepted and will be invalid . The scanned image of deposit copy of earnest money deposit , through SB Collect , to be uploaded along with the tender,
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-If EMD waiver is sought, Please specify against which relevant type of Document along with its Document No &amp; validity period, the waiver is sought.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-The steps of EMD Submission are mentioned herewith below, *
-* The steps of EMD Submission are as below,
-1. Login to https://www.onlinesbi.sbi/sbicollect
-2. Click on select category as “ PSU-Public Sector Undertaking”
-3. Filter by State as “Maharashtra “ in the drop down menu. Thereafter select “PSU-Public Sector Undertaking” name as Hindustan Aeronautics Limited and Click.
-4. Select Payment Category as “Receipt from Supplier/Vendors/Contractors/Others ” and Fill-up the respective information correctly and Select purpose of Transfer as “EMD / Security Deposit / Tender fee ( As applicable) , Select “ Nature of Supplier” as applicable . fill details correctly and Click “ Submit”.
-5. If all details entered are correctly populated , click “NEXT” to proceed. Verify the payment Details , Click “ Next” to proceed.
-6. Make payment as per your convenience . ( Options available are payment of fees through Net Banking / Card Payments/ Other Payment Modes 
-7. Print Receipt and upload in the Tender portal.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1038,7 +892,7 @@
         <rFont val="Gadugi"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">1. User to fill the sheet by selecting options from drop down menu in "Compliance" header.
+      <t xml:space="preserve">1. User to fill the sheet by selecting options from drop down menu in "Compliance" head.
 </t>
     </r>
     <r>
@@ -1118,12 +972,209 @@
       <t>6. This CHECK LIST shall be part of Provisioning Approval duly signed &amp; stamped.</t>
     </r>
   </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Provisioning File</t>
+  </si>
+  <si>
+    <t>Description of File</t>
+  </si>
+  <si>
+    <t>Subject of File</t>
+  </si>
+  <si>
+    <t>Provide the Subject of File here</t>
+  </si>
+  <si>
+    <t>Direct Project Material or Production Material</t>
+  </si>
+  <si>
+    <t>Indigenisation or Development of Alternate Source of Project Materials</t>
+  </si>
+  <si>
+    <t>Overhead Materials or Commercial Materials, Stock Items</t>
+  </si>
+  <si>
+    <t>Non-stock Items</t>
+  </si>
+  <si>
+    <t>Tool and Gauges</t>
+  </si>
+  <si>
+    <t>Ground Handling Equipment (GHE) - Ground Support Equipment (GSE)- Bay Support Equipment (BSE)</t>
+  </si>
+  <si>
+    <t>Maintenance Spares</t>
+  </si>
+  <si>
+    <t>Vehicle Spares</t>
+  </si>
+  <si>
+    <t>Civil Engineering Requirements</t>
+  </si>
+  <si>
+    <t>Welfare Items</t>
+  </si>
+  <si>
+    <t>Capital Equipment</t>
+  </si>
+  <si>
+    <t>Email/Contact details For Single/Email tender /OEM/Licensor/Proprietary tender/Limited Tenders</t>
+  </si>
+  <si>
+    <t>For floating Tenders having value above INR 5.00Lakhs &amp; up to INR 200.00 Crs, for GTE  outside GeM/Eproc and to Non Clocal/Foreign Suppliers permission is required from concerned Ministry for floating tender.</t>
+  </si>
+  <si>
+    <t>Provisioning CPA as per DOP-2025 &amp; PM Iss-4.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFA Name, Grade &amp; Designation Information
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(To be provided in Remarks Column)</t>
+    </r>
+  </si>
+  <si>
+    <t>Reason for Provisioning</t>
+  </si>
+  <si>
+    <t>Provide the brief reason for Provisoining action</t>
+  </si>
+  <si>
+    <t>Provide Budget Head reference No here</t>
+  </si>
+  <si>
+    <t>Reason for requirements recorded with refrences in Provisioining Note</t>
+  </si>
+  <si>
+    <t>GeM Non Availability Report enclosed for tendering out of GeM &amp; GEM Custom Bidding</t>
+  </si>
+  <si>
+    <t>Submission of Tender In Bid System.</t>
+  </si>
+  <si>
+    <t>GEM-Custom bid</t>
+  </si>
+  <si>
+    <t>Same requirement not Raised within Six Months</t>
+  </si>
+  <si>
+    <t>Same requirement Raised within Six Months of previous MPR leads to splitting of requirement in such cases Permission from Head of Division to be obatined for tendering on account of critical requirement for Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Modality </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EMD shall be paid only through SB Collect portal in online mode to Hindustan Aeronautics Ltd, Nasik Division. Further , deposit of the amount in any other form will not be accepted and will be invalid . The scanned image of deposit copy of earnest money deposit , through SB Collect , to be uploaded along with the tender,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+If EMD waiver is sought, Please specify against which relevant type of Document along with its Document No &amp; validity period, the waiver is sought.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+The steps of EMD Submission are mentioned herewith below, *
+* The steps of EMD Submission are as below,
+1. Login to https://www.onlinesbi.sbi/sbicollect
+2. Click on select category as “ PSU-Public Sector Undertaking”
+3. Filter by State as “Maharashtra “ in the drop down menu. Thereafter select “PSU-Public Sector Undertaking” name as Hindustan Aeronautics Limited and Click.
+4. Select Payment Category as “Receipt from Supplier/Vendors/Contractors/Others ” and Fill-up the respective information correctly and Select purpose of Transfer as “EMD / Security Deposit / Tender fee ( As applicable) , Select “ Nature of Supplier” as applicable . fill details correctly and Click “ Submit”.
+5. If all details entered are correctly populated , click “NEXT” to proceed. Verify the payment Details , Click “ Next” to proceed.
+6. Make payment as per your convenience . ( Options available are payment of fees through Net Banking / Card Payments/ Other Payment Modes 
+7. Print Receipt and upload in the Tender portal.</t>
+    </r>
+  </si>
+  <si>
+    <t>In Case of Three Bid Pre Meeting</t>
+  </si>
+  <si>
+    <t>In Case of Three Bid Pre Meeting requireed Yes/No provide date for prebid</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>category (tech/Commercial)</t>
+  </si>
+  <si>
+    <t>MPR Ref</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>Mentioned</t>
+  </si>
+  <si>
+    <t>COMPLIANCE 
+(Choose from Drop Down Menu)</t>
+  </si>
+  <si>
+    <t>Goods</t>
+  </si>
+  <si>
+    <t>Technical Estimate</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Composite</t>
+  </si>
+  <si>
+    <t>Yes-CPA is Level I</t>
+  </si>
+  <si>
+    <t>Check list Part to be filled by Indnetor</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>Supply of Goods &amp; Services (AMC/CAMC)</t>
+  </si>
+  <si>
+    <t>Check list Part to be filled by Indnetor &amp; used in Tender doc creation &amp; TEC report</t>
+  </si>
+  <si>
+    <t>Check list Part to be filled by Indnetor &amp; used in Tender doc creation &amp; commercial Evalaution by tendering Group</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1296,6 +1347,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1323,7 +1382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1840,11 +1899,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -2063,26 +2133,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2139,15 +2189,111 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2190,69 +2336,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2533,11 +2616,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="38.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" customWidth="1"/>
@@ -2546,37 +2629,44 @@
     <col min="4" max="4" width="111.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" customWidth="1"/>
     <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" style="97"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
       <c r="F1" s="27" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="231" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
-        <v>228</v>
-      </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="106"/>
-    </row>
-    <row r="3" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="G1" s="98" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1" s="99" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="231" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="132"/>
+    </row>
+    <row r="3" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="82" t="s">
-        <v>141</v>
+      <c r="B3" s="76" t="s">
+        <v>140</v>
       </c>
       <c r="C3" s="49" t="s">
         <v>1</v>
@@ -2585,72 +2675,88 @@
         <v>2</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>54</v>
+        <v>235</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="H3" s="96"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="77" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="84" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="85" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="86"/>
+      <c r="C4" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="80" t="s">
+        <v>232</v>
+      </c>
       <c r="F4" s="53" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="H4" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="D5" s="76" t="s">
-        <v>152</v>
-      </c>
-      <c r="E5" s="77"/>
+      <c r="E5" s="71" t="s">
+        <v>233</v>
+      </c>
       <c r="F5" s="32" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="H5" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="73" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="E6" s="81"/>
+      <c r="E6" s="75" t="s">
+        <v>234</v>
+      </c>
       <c r="F6" s="47" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="H6" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>1</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>217</v>
@@ -2659,185 +2765,220 @@
         <v>220</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>218</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H7" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>2</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="77"/>
+        <v>124</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>236</v>
+      </c>
       <c r="F8" s="25"/>
       <c r="G8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H8" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>3</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="77"/>
+        <v>156</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>212</v>
+      </c>
       <c r="F9" s="25"/>
       <c r="G9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H9" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <v>4</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="91"/>
+        <v>58</v>
+      </c>
+      <c r="E10" s="85" t="s">
+        <v>237</v>
+      </c>
       <c r="F10" s="44"/>
       <c r="G10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H10" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>5</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="E11" s="77"/>
+      <c r="E11" s="71" t="s">
+        <v>238</v>
+      </c>
       <c r="F11" s="28" t="s">
         <v>219</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H11" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>6</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F12" s="25"/>
       <c r="G12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H12" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>7</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>110</v>
-      </c>
       <c r="E13" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F13" s="25"/>
       <c r="G13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H13" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>8</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="26">
-        <v>0.18</v>
+      <c r="E14" s="26" t="s">
+        <v>239</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H14" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>9</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H15" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>10</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>215</v>
@@ -2846,63 +2987,74 @@
         <v>216</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H16" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>11</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="77"/>
+        <v>104</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>240</v>
+      </c>
       <c r="F17" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H17" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>12</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>159</v>
-      </c>
       <c r="E18" s="24" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H18" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>13</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>224</v>
@@ -2911,127 +3063,145 @@
         <v>225</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H19" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>14</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>221</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F20" s="25"/>
       <c r="G20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H20" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>15</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>146</v>
-      </c>
       <c r="E21" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H21" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>16</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="23" t="s">
-        <v>162</v>
-      </c>
       <c r="E22" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22" s="25"/>
       <c r="G22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H22" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="20">
         <v>17</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="H23" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>18</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H24" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>19</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>50</v>
@@ -3040,1383 +3210,1556 @@
         <v>214</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25" s="25"/>
       <c r="G25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H25" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>20</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H26" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="20">
         <v>21</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="H27" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>22</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="D28" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="F28" s="59" t="s">
-        <v>174</v>
-      </c>
       <c r="G28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H28" s="96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A29" s="63">
         <v>1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="65" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" s="86"/>
+        <v>124</v>
+      </c>
+      <c r="E29" s="80" t="s">
+        <v>236</v>
+      </c>
       <c r="F29" s="67"/>
       <c r="G29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H29" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H30" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>3</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>223</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H31" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>4</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+        <v>59</v>
+      </c>
+      <c r="H32" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="63">
         <v>5</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>24</v>
+        <v>228</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H33" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>6</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>132</v>
+        <v>61</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="87.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H34" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>7</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35" s="29" t="s">
-        <v>123</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="F35" s="9"/>
       <c r="G35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H35" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="88.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>8</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="63">
+        <v>9</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="9"/>
-      <c r="G36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>9</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E37" s="77"/>
-      <c r="F37" s="29" t="s">
-        <v>166</v>
-      </c>
+      <c r="E37" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="9"/>
       <c r="G37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H37" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>10</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" s="71" t="s">
+        <v>243</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H38" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>11</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>36</v>
+        <v>61</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F39" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="F39" s="29" t="s">
+        <v>117</v>
+      </c>
       <c r="G39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H39" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>12</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+        <v>59</v>
+      </c>
+      <c r="H40" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="63">
         <v>13</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="90" t="s">
-        <v>4</v>
+        <v>42</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="29" t="s">
-        <v>117</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="F41" s="9"/>
       <c r="G41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H41" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>14</v>
       </c>
       <c r="B42" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="90" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="F42" s="29" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H42" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>15</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>111</v>
+      <c r="C43" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="84" t="s">
+        <v>175</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="330" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H43" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>16</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="G44" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="330" x14ac:dyDescent="0.25">
+      <c r="A45" s="63">
+        <v>17</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="G44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="171" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>17</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="F45" s="29" t="s">
+        <v>163</v>
+      </c>
       <c r="G45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="99.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H45" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="171" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>18</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+        <v>59</v>
+      </c>
+      <c r="H46" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="88">
         <v>19</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>62</v>
+      <c r="B47" s="88" t="s">
+        <v>61</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>226</v>
+        <v>31</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="68">
+        <v>59</v>
+      </c>
+      <c r="H47" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="57" x14ac:dyDescent="0.25">
+      <c r="A48" s="93">
         <v>20</v>
       </c>
-      <c r="B48" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="71" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="72">
-        <v>180</v>
-      </c>
-      <c r="F48" s="73"/>
+      <c r="B48" s="93" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="10"/>
       <c r="G48" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="99.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="92">
+      <c r="H48" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="94">
         <v>21</v>
       </c>
-      <c r="B49" s="93" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="10"/>
+      <c r="B49" s="95" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="92">
+        <v>180</v>
+      </c>
+      <c r="F49" s="91"/>
       <c r="G49" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A50" s="92">
+      <c r="H49" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>22</v>
       </c>
-      <c r="B50" s="93" t="s">
-        <v>62</v>
+      <c r="B50" s="86" t="s">
+        <v>61</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="94" t="s">
-        <v>64</v>
+        <v>26</v>
+      </c>
+      <c r="E50" s="87" t="s">
+        <v>63</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H50" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>23</v>
       </c>
-      <c r="B51" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="C51" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="B51" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="10"/>
       <c r="G51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="H51" s="96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>24</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="7" t="s">
+      <c r="B52" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" t="s">
+        <v>60</v>
+      </c>
+      <c r="H52" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="57" x14ac:dyDescent="0.25">
+      <c r="A53" s="63">
+        <v>25</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E52" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>25</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="E53" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H53" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>26</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="128.25" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H54" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>27</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>39</v>
+        <v>227</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="128.25" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H55" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="129" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>28</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G56" t="s">
+        <v>60</v>
+      </c>
+      <c r="H56" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="128.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="63">
+        <v>29</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D57" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>29</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="E57" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H57" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>30</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H58" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>31</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H59" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>32</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G60" t="s">
+        <v>60</v>
+      </c>
+      <c r="H60" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="57" x14ac:dyDescent="0.25">
+      <c r="A61" s="63">
+        <v>33</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D61" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E60" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="G60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>33</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="E61" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H61" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>34</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H62" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>35</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H63" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>36</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G64" t="s">
+        <v>60</v>
+      </c>
+      <c r="H64" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="57" x14ac:dyDescent="0.25">
+      <c r="A65" s="63">
+        <v>37</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>37</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>139</v>
-      </c>
       <c r="E65" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H65" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G66" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H66" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="57" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>39</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G67" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="H67" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>40</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G68" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="57" x14ac:dyDescent="0.25">
+      <c r="A69" s="63">
+        <v>41</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D69" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="E69" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H69" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="39" customFormat="1" ht="57" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>42</v>
+      </c>
+      <c r="B70" s="34" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" s="39" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>41</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C69" s="35" t="s">
+      <c r="C70" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="D70" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="D69" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="F69" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="G69" s="39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="101" t="s">
+      <c r="E70" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H70" s="96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="127" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="128"/>
+      <c r="C72" s="129"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="107"/>
+      <c r="C73" s="107"/>
+      <c r="D73" s="107"/>
+      <c r="E73" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="102"/>
-      <c r="C71" s="103"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="19"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="124" t="s">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="125"/>
-      <c r="C72" s="125"/>
-      <c r="D72" s="125"/>
-      <c r="E72" s="128" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="124" t="s">
+      <c r="B74" s="107"/>
+      <c r="C74" s="107"/>
+      <c r="D74" s="107"/>
+      <c r="E74" s="110"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="125"/>
-      <c r="C73" s="125"/>
-      <c r="D73" s="125"/>
-      <c r="E73" s="128"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="124" t="s">
+      <c r="B75" s="107"/>
+      <c r="C75" s="107"/>
+      <c r="D75" s="107"/>
+      <c r="E75" s="110"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="125"/>
-      <c r="C74" s="125"/>
-      <c r="D74" s="125"/>
-      <c r="E74" s="128"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="124" t="s">
+      <c r="B76" s="107"/>
+      <c r="C76" s="107"/>
+      <c r="D76" s="107"/>
+      <c r="E76" s="110"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="125"/>
-      <c r="C75" s="125"/>
-      <c r="D75" s="125"/>
-      <c r="E75" s="128"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="124" t="s">
+      <c r="B77" s="107"/>
+      <c r="C77" s="107"/>
+      <c r="D77" s="107"/>
+      <c r="E77" s="110"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="125"/>
-      <c r="C76" s="125"/>
-      <c r="D76" s="125"/>
-      <c r="E76" s="128"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="124" t="s">
+      <c r="B78" s="107"/>
+      <c r="C78" s="107"/>
+      <c r="D78" s="107"/>
+      <c r="E78" s="110"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="125"/>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="128"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="124" t="s">
+      <c r="B79" s="107"/>
+      <c r="C79" s="107"/>
+      <c r="D79" s="107"/>
+      <c r="E79" s="110"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="106" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="125"/>
-      <c r="C78" s="125"/>
-      <c r="D78" s="125"/>
-      <c r="E78" s="128"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="124" t="s">
+      <c r="B80" s="107"/>
+      <c r="C80" s="107"/>
+      <c r="D80" s="107"/>
+      <c r="E80" s="110"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="125"/>
-      <c r="C79" s="125"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="128"/>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="126" t="s">
+      <c r="B81" s="109"/>
+      <c r="C81" s="109"/>
+      <c r="D81" s="109"/>
+      <c r="E81" s="111"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="127"/>
-      <c r="C80" s="127"/>
-      <c r="D80" s="127"/>
-      <c r="E80" s="129"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="98" t="s">
+      <c r="B82" s="125"/>
+      <c r="C82" s="125"/>
+      <c r="D82" s="125"/>
+      <c r="E82" s="126"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="121"/>
+      <c r="B83" s="122"/>
+      <c r="C83" s="122"/>
+      <c r="D83" s="122"/>
+      <c r="E83" s="123"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="112" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="99"/>
-      <c r="C81" s="99"/>
-      <c r="D81" s="99"/>
-      <c r="E81" s="100"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="95"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="96"/>
-      <c r="D82" s="96"/>
-      <c r="E82" s="97"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="109" t="s">
+      <c r="B84" s="113"/>
+      <c r="C84" s="113"/>
+      <c r="D84" s="113"/>
+      <c r="E84" s="114"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="112" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="110"/>
-      <c r="C83" s="110"/>
-      <c r="D83" s="110"/>
-      <c r="E83" s="111"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="109" t="s">
+      <c r="B85" s="113"/>
+      <c r="C85" s="113"/>
+      <c r="D85" s="113"/>
+      <c r="E85" s="114"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="110"/>
-      <c r="C84" s="110"/>
-      <c r="D84" s="110"/>
-      <c r="E84" s="111"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="109" t="s">
+      <c r="B86" s="113"/>
+      <c r="C86" s="113"/>
+      <c r="D86" s="113"/>
+      <c r="E86" s="114"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="110"/>
-      <c r="C85" s="110"/>
-      <c r="D85" s="110"/>
-      <c r="E85" s="111"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="109" t="s">
+      <c r="B87" s="113"/>
+      <c r="C87" s="113"/>
+      <c r="D87" s="113"/>
+      <c r="E87" s="114"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="110"/>
-      <c r="C86" s="110"/>
-      <c r="D86" s="110"/>
-      <c r="E86" s="111"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="109" t="s">
+      <c r="B88" s="113"/>
+      <c r="C88" s="113"/>
+      <c r="D88" s="113"/>
+      <c r="E88" s="114"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="112" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="110"/>
-      <c r="C87" s="110"/>
-      <c r="D87" s="110"/>
-      <c r="E87" s="111"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="109" t="s">
+      <c r="B89" s="113"/>
+      <c r="C89" s="113"/>
+      <c r="D89" s="113"/>
+      <c r="E89" s="114"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="110"/>
-      <c r="C88" s="110"/>
-      <c r="D88" s="110"/>
-      <c r="E88" s="111"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="115" t="s">
+      <c r="B90" s="116"/>
+      <c r="C90" s="116"/>
+      <c r="D90" s="116"/>
+      <c r="E90" s="117"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="118" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="116"/>
-      <c r="C89" s="116"/>
-      <c r="D89" s="116"/>
-      <c r="E89" s="117"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="118" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" s="119"/>
-      <c r="C90" s="119"/>
-      <c r="D90" s="119"/>
-      <c r="E90" s="120"/>
-    </row>
-    <row r="91" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="14">
+      <c r="B91" s="119"/>
+      <c r="C91" s="119"/>
+      <c r="D91" s="119"/>
+      <c r="E91" s="120"/>
+    </row>
+    <row r="92" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="14">
         <v>1</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C91" s="112"/>
-      <c r="D91" s="113"/>
-      <c r="E91" s="114"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="14">
-        <v>2</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" s="112"/>
-      <c r="D92" s="113"/>
-      <c r="E92" s="114"/>
+      <c r="B92" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="100"/>
+      <c r="D92" s="101"/>
+      <c r="E92" s="102"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" s="112"/>
-      <c r="D93" s="113"/>
-      <c r="E93" s="114"/>
+        <v>88</v>
+      </c>
+      <c r="C93" s="100"/>
+      <c r="D93" s="101"/>
+      <c r="E93" s="102"/>
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" s="112"/>
-      <c r="D94" s="113"/>
-      <c r="E94" s="114"/>
+        <v>89</v>
+      </c>
+      <c r="C94" s="100"/>
+      <c r="D94" s="101"/>
+      <c r="E94" s="102"/>
     </row>
     <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C95" s="112"/>
-      <c r="D95" s="113"/>
-      <c r="E95" s="114"/>
+        <v>90</v>
+      </c>
+      <c r="C95" s="100"/>
+      <c r="D95" s="101"/>
+      <c r="E95" s="102"/>
     </row>
     <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="14">
+        <v>5</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" s="100"/>
+      <c r="D96" s="101"/>
+      <c r="E96" s="102"/>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="14">
         <v>6</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B97" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" s="100"/>
+      <c r="D97" s="101"/>
+      <c r="E97" s="102"/>
+    </row>
+    <row r="98" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A98" s="14">
+        <v>7</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" s="100"/>
+      <c r="D98" s="101"/>
+      <c r="E98" s="102"/>
+    </row>
+    <row r="99" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+      <c r="A99" s="14">
+        <v>8</v>
+      </c>
+      <c r="B99" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="112"/>
-      <c r="D96" s="113"/>
-      <c r="E96" s="114"/>
-    </row>
-    <row r="97" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A97" s="14">
-        <v>7</v>
-      </c>
-      <c r="B97" s="16" t="s">
+      <c r="C99" s="100"/>
+      <c r="D99" s="101"/>
+      <c r="E99" s="102"/>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="14">
+        <v>9</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C100" s="100"/>
+      <c r="D100" s="101"/>
+      <c r="E100" s="102"/>
+    </row>
+    <row r="101" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="14">
+        <v>10</v>
+      </c>
+      <c r="B101" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="112"/>
-      <c r="D97" s="113"/>
-      <c r="E97" s="114"/>
-    </row>
-    <row r="98" spans="1:5" ht="63" x14ac:dyDescent="0.25">
-      <c r="A98" s="14">
-        <v>8</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C98" s="112"/>
-      <c r="D98" s="113"/>
-      <c r="E98" s="114"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="14">
-        <v>9</v>
-      </c>
-      <c r="B99" s="16" t="s">
+      <c r="C101" s="100"/>
+      <c r="D101" s="101"/>
+      <c r="E101" s="102"/>
+    </row>
+    <row r="102" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="14">
+        <v>11</v>
+      </c>
+      <c r="B102" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C99" s="112"/>
-      <c r="D99" s="113"/>
-      <c r="E99" s="114"/>
-    </row>
-    <row r="100" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="14">
-        <v>10</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C100" s="112"/>
-      <c r="D100" s="113"/>
-      <c r="E100" s="114"/>
-    </row>
-    <row r="101" spans="1:5" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="14">
-        <v>11</v>
-      </c>
-      <c r="B101" s="16" t="s">
+      <c r="C102" s="100"/>
+      <c r="D102" s="101"/>
+      <c r="E102" s="102"/>
+    </row>
+    <row r="103" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A103" s="14">
+        <v>12</v>
+      </c>
+      <c r="B103" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C101" s="112"/>
-      <c r="D101" s="113"/>
-      <c r="E101" s="114"/>
-    </row>
-    <row r="102" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="14">
-        <v>12</v>
-      </c>
-      <c r="B102" s="16" t="s">
+      <c r="C103" s="100"/>
+      <c r="D103" s="101"/>
+      <c r="E103" s="102"/>
+    </row>
+    <row r="104" spans="1:5" ht="63" x14ac:dyDescent="0.25">
+      <c r="A104" s="14">
+        <v>13</v>
+      </c>
+      <c r="B104" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C102" s="112"/>
-      <c r="D102" s="113"/>
-      <c r="E102" s="114"/>
-    </row>
-    <row r="103" spans="1:5" ht="63" x14ac:dyDescent="0.25">
-      <c r="A103" s="14">
-        <v>13</v>
-      </c>
-      <c r="B103" s="16" t="s">
+      <c r="C104" s="100"/>
+      <c r="D104" s="101"/>
+      <c r="E104" s="102"/>
+    </row>
+    <row r="105" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="14">
+        <v>14</v>
+      </c>
+      <c r="B105" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C103" s="112"/>
-      <c r="D103" s="113"/>
-      <c r="E103" s="114"/>
-    </row>
-    <row r="104" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A104" s="14">
-        <v>14</v>
-      </c>
-      <c r="B104" s="16" t="s">
+      <c r="C105" s="100"/>
+      <c r="D105" s="101"/>
+      <c r="E105" s="102"/>
+    </row>
+    <row r="106" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="14">
+        <v>15</v>
+      </c>
+      <c r="B106" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C104" s="112"/>
-      <c r="D104" s="113"/>
-      <c r="E104" s="114"/>
-    </row>
-    <row r="105" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="14">
-        <v>15</v>
-      </c>
-      <c r="B105" s="16" t="s">
+      <c r="C106" s="100"/>
+      <c r="D106" s="101"/>
+      <c r="E106" s="102"/>
+    </row>
+    <row r="107" spans="1:5" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="14">
+        <v>16</v>
+      </c>
+      <c r="B107" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C105" s="112"/>
-      <c r="D105" s="113"/>
-      <c r="E105" s="114"/>
-    </row>
-    <row r="106" spans="1:5" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="14">
-        <v>16</v>
-      </c>
-      <c r="B106" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C106" s="121"/>
-      <c r="D106" s="122"/>
-      <c r="E106" s="123"/>
-    </row>
-    <row r="107" spans="1:5" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A107" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="B107" s="30" t="s">
-        <v>192</v>
-      </c>
+      <c r="C107" s="103"/>
+      <c r="D107" s="104"/>
+      <c r="E107" s="105"/>
     </row>
     <row r="108" spans="1:5" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A108" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B108" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A109" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>194</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A110" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" s="30" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="39">
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="C97:E97"/>
     <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C107:E107"/>
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="A74:D74"/>
     <mergeCell ref="A75:D75"/>
@@ -4425,174 +4768,167 @@
     <mergeCell ref="A78:D78"/>
     <mergeCell ref="A79:D79"/>
     <mergeCell ref="A80:D80"/>
-    <mergeCell ref="E72:E80"/>
-    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E73:E81"/>
     <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C103:E103"/>
     <mergeCell ref="C94:E94"/>
     <mergeCell ref="C95:E95"/>
     <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
   </mergeCells>
-  <dataValidations xWindow="1368" yWindow="411" count="44">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a__x000a_For email tendering Provide waiver from Head of Division for cases above INR 2.00 lakhs &amp; GeM Non availabilioty Report" sqref="E31" xr:uid="{8BE4FC37-D241-412D-BFF6-F3F35349DD69}">
-      <formula1>"e-mail,E-Proc,GEM-Std.,GEM-Custom bid,GEM-Proprietary,Committee Purchase"</formula1>
+  <dataValidations xWindow="1368" yWindow="411" count="45">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a__x000a_For email tendering Provide waiver from Head of Division for cases above INR 2.00 lakhs &amp; GeM Non availabilioty Report" sqref="E31">
+      <formula1>"e-mail,E-Proc,GEM Limited,GEM SINGLE-NOMINATION,GEM-Std Catalog,GEM L1 Direct Purchase,GEM Direct Purchase,GEM-Custom bid,GEM-Proprietary,Committee Purchase"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E31" xr:uid="{59B530A0-CF86-43A1-9E82-5EA310490007}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E31">
       <formula1>"Open,Limited,Licensor,OEM,Proprietory,Global"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E32" xr:uid="{F7A973C9-C0D9-41B9-A9C6-836202B1B475}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E32">
       <formula1>"Single Bid,Two Bid, Three bid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_For email tendering Provide waiver from Head of Division for cases above INR 2.00 lakhs in Remarks Column" sqref="E21" xr:uid="{5F18BB6D-65D4-454E-B055-60B4738045E1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_For email tendering Provide waiver from Head of Division for cases above INR 2.00 lakhs in Remarks Column" sqref="E21">
       <formula1>"Yes-Permission for waiver Enclosed, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_And Provide DOP-2025 Reference in Remarks Column" sqref="E17" xr:uid="{8EEDC492-7AA2-4050-BF67-13008B38173C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_And Provide DOP-2025 Reference in Remarks Column" sqref="E17">
       <formula1>"YES-CPA is BOARD, YES-CPA is CMD, YES-CPA is PC, Yes-CPA is AC,Yes-CFA is CEO(MC),Yes-CPA is Level I, Yes-CPA is Level II, Yes-CPA is Level III, NO, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_And Provide DOP-2025 Reference in Remarks Column, if applicable" sqref="E18" xr:uid="{40F7EFED-9032-4C6F-ACBB-B3F68E3786AF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_And Provide DOP-2025 Reference in Remarks Column, if applicable" sqref="E18">
       <formula1>"NA, Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_For AMC Select Services" sqref="E29 E8" xr:uid="{95BA4392-1252-40F4-B109-E40763C16B80}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_For AMC Select Services" sqref="E29 E8">
       <formula1>"Goods, Services, Goods + Services"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E17:E18" xr:uid="{4C0FD55A-10B8-4DA7-9668-F83E97DD62D3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E17:E18">
       <formula1>"Line Wise,Package Wise"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note." sqref="E25" xr:uid="{EDBB6B3A-8E53-4489-B16D-FC738C1AC02A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note." sqref="E25">
       <formula1>"YES/To be arranged by Purchase, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E36" xr:uid="{0856AC94-2513-4B5D-9D53-AF0572F1F783}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E37">
       <formula1>"Yes, No, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E51:E69" xr:uid="{64D48433-3B85-4BB3-85B9-8D83B93DAD3C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E52:E70">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note" sqref="E24" xr:uid="{BFF3C7C5-5228-4B02-84E2-2860DCF7A791}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note" sqref="E24">
       <formula1>"NA,Yes"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E34" xr:uid="{47891BFC-0065-45AA-9D78-FF2A627050E2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E35">
       <formula1>"FOR HAL Nasik Site, Ex WORKS Supplier end, AT Suggested Site as per Tender Condt.."</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E30" xr:uid="{0BCFBD37-62CA-4589-86B7-5415342A3027}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E30">
       <formula1>"Open,Limited,Licensor,OEM,Proprietory,Global,Single Nominated Source"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_PRovide Details of Budget Head reference no. in Remarks Column" sqref="E11" xr:uid="{0B9BAAB1-6023-40AD-A2CC-1E15A9568017}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_PRovide Details of Budget Head reference no. in Remarks Column" sqref="E11">
       <formula1>"Revenue,Capital,Reapir &amp; Maintenance,DRE,CSR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E10" xr:uid="{D43778A2-9E92-4FE9-AFBB-005E41D4C24A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E10">
       <formula1>"Rate contract,LPP basis,Technical Estimate,LPP+TE,Based on BQs (3 BQs basis/ Single BQ Basis),GEM quote"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E14" xr:uid="{114EA8D1-FA09-401D-931C-4442327E0865}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E14">
       <formula1>"0%,5%,12%,18%,28%, Composite"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Privde Site Readiness Days after PO placement in Remarks Column" sqref="E42" xr:uid="{B9F22260-DB78-4B85-BB26-4E5A82EDA330}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Privde Site Readiness Days after PO placement in Remarks Column" sqref="E43">
       <formula1>"NA, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E13" xr:uid="{9AE41A9B-9801-4F68-83DF-3F1FB1959ABE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E13">
       <formula1>"YES-Included in MPR, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E12" xr:uid="{E74AB294-E657-4518-AD7B-A5466EB4FEC7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E12">
       <formula1>"No, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E48" xr:uid="{0BCBAB98-CAA6-4057-BDE1-5C849247A967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E49">
       <formula1>"120,150,180"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_PRovide CFA Name &amp; Designation in Remarks Column" sqref="E16" xr:uid="{C3E0C9D3-5A54-48C0-A604-A588346A8F83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_PRovide CFA Name &amp; Designation in Remarks Column" sqref="E16">
       <formula1>"NA,Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If, Yes, Provide from where Price is Recoverrable in Remarks column" sqref="E26" xr:uid="{2E012687-7B29-4AB2-8CBF-56432DC6F75F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If, Yes, Provide from where Price is Recoverrable in Remarks column" sqref="E26">
       <formula1>"NA, YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E33" xr:uid="{942F37DE-8312-48BB-A49B-6D8C83870666}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E34">
       <formula1>"Line Wise,Package Wise"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide TOD in no of Days in Reamrks column if less or more than 21 days is required" sqref="E38" xr:uid="{7304A109-E73C-463F-90BA-553DF59C7D52}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide TOD in no of Days in Reamrks column if less or more than 21 days is required" sqref="E39">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E40 E45:E47 E49:E50" xr:uid="{BC0D5F00-A8A5-47FC-AB94-745DF511B6C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E41 E46:E48 E50:E51">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide expected Warranty Support Response Time in Remarks column" sqref="E44" xr:uid="{58F953B7-2866-4B0A-99FE-67177BAC14EE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide expected Warranty Support Response Time in Remarks column" sqref="E45">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Certification Requirements in Remarks Column if applicable" sqref="E43" xr:uid="{E4B62731-D9BD-4837-93E9-F81885713A53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Certification Requirements in Remarks Column if applicable" sqref="E44">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Inspections conditions in Remarks column if some other condt is required" sqref="E41" xr:uid="{880CD5B1-DA34-473B-933E-9DE305C9CE2C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Inspections conditions in Remarks column if some other condt is required" sqref="E42">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Delivery Schedule in No of Days in Remarks Column" sqref="E35" xr:uid="{E1E68D28-B254-40EE-A6CA-3A5CE69BC75B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Delivery Schedule in No of Days in Remarks Column" sqref="E36">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Email and Contact No of Proposed vendors in Remarks column" sqref="E23" xr:uid="{4B867E55-9C57-4AB2-866A-A8E51843EEA1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Email and Contact No of Proposed vendors in Remarks column" sqref="E23">
       <formula1>"NA, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide deatiled PDI Condt in Remarks Column" sqref="E39" xr:uid="{3D7C52F4-B780-4E1C-9717-F249F13DCA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide deatiled PDI Condt in Remarks Column" sqref="E40">
       <formula1>"Clause to be included in Tender T&amp;C, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, Enclose GEM Non Availability Report with Provisiosning Approaval" sqref="E20" xr:uid="{ADA09141-B770-4694-8462-79665CFA9357}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, Enclose GEM Non Availability Report with Provisiosning Approaval" sqref="E20">
       <formula1>"NO,YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E16" xr:uid="{DB12164A-EC78-4F74-8821-AC9DDCAF5762}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E16">
       <formula1>"NA, Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Provide MPR/SPR/CAR No &amp; date in Remarks Column" sqref="E4" xr:uid="{1E25146E-2CD5-4469-9355-6F38916A0D20}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Provide MPR/SPR/CAR No &amp; date in Remarks Column" sqref="E4">
       <formula1>"MPR Ref,SPR Ref,CAR Ref"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="In case Yes Provide the Cost of Repair/OH/Servicing/AMC/CAMC in % terms of the cost of purcshase of the item in Remarks Column" sqref="E15" xr:uid="{F4B69FC8-148E-46BA-AAE2-F19F5A08EA4E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="In case Yes Provide the Cost of Repair/OH/Servicing/AMC/CAMC in % terms of the cost of purcshase of the item in Remarks Column" sqref="E15">
       <formula1>"NA, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Provide Value of Proposal in Remraks Column and Select currency from Drop Down" sqref="E5" xr:uid="{9516C7B1-D574-4ABF-BA4A-786E9673E86B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Provide Value of Proposal in Remraks Column and Select currency from Drop Down" sqref="E5">
       <formula1>"INR,USD,GBP,EURO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note." sqref="E22" xr:uid="{BD239029-5FB1-4B54-AE1C-A514CE4D1815}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_If Yes, take approval from from Competent authority in provisioning Note." sqref="E22">
       <formula1>"NA, Exemption obtained in Provisioning Note"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select From Drop Down Menu" sqref="E37" xr:uid="{A3B77BE2-7DAB-4ACD-A7ED-9A90A4759E49}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select From Drop Down Menu" sqref="E38">
       <formula1>"Supply of Goods Only,Supply of Goods-Installation-Testing &amp; Commissining,Supply of Goods-Installation-Testing-Training &amp; Commissioning,Supply of Services,Supply of Goods &amp; Services (AMC/CAMC)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E27:E28" xr:uid="{D66B5354-1EFE-4DD7-973F-08DDA735143D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E27:E28">
       <formula1>"NA, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E6" xr:uid="{7E48A289-5309-49D3-A7DE-57AF5E871192}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E6">
       <formula1>"Mentioned, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide the brief reason for Provisoining action" sqref="E7" xr:uid="{4C140AE3-CDB5-4AE3-81BA-6ABE649C2343}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide the brief reason for Provisoining action" sqref="E7">
       <formula1>"NA, YES, NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Head of Division Approval in Provisioining note, if applicable" sqref="E19" xr:uid="{157ECCE7-83FA-436B-A964-37EB65CC231C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_Provide Head of Division Approval in Provisioining note, if applicable" sqref="E19">
       <formula1>"NA, YES"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="If Yes,  Permission from Head of Division to be obatined for critical requirement of Production in provisioning Note" sqref="E19" xr:uid="{CAB73E38-7C18-42C6-8961-C6BF525F940F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="If Yes,  Permission from Head of Division to be obatined for critical requirement of Production in provisioning Note" sqref="E19">
       <formula1>"NA, YES"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu" sqref="E33">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.43307086614173229" right="0.19685039370078741" top="0.55118110236220474" bottom="0.23622047244094491" header="0.31496062992125984" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="28" max="5" man="1"/>
-    <brk id="43" max="5" man="1"/>
+    <brk id="44" max="5" man="1"/>
   </rowBreaks>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="1368" yWindow="411" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_" xr:uid="{20E2077B-BD01-45E4-A4CD-3DAFC5BB74F4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select from Drop Down Menu_x000a_">
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$13</xm:f>
           </x14:formula1>
@@ -4605,11 +4941,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421DC6E4-05DA-4775-A002-57A15C204517}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.28515625" style="87" customWidth="1"/>
+    <col min="1" max="1" width="53.28515625" style="81" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4618,63 +4954,63 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="81" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="82" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="83" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="82" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="82" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="82" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="82" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="82" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="81" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="82" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="82" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="82" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="88" t="s">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
